--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487915_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487915_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7307</v>
+        <v>3.8878</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3553</v>
+        <v>4.2482</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6246</v>
+        <v>-0.3604</v>
       </c>
       <c r="G2" t="n">
         <v>0.9494</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8025</v>
+        <v>-0.6454</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2643</v>
+        <v>-0.3714</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5382</v>
+        <v>-0.274</v>
       </c>
       <c r="V2" t="n">
         <v>2.3351</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. DUKE TOUSSAINT</t>
+          <t>D. RAMÍREZ SÁNCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3812</v>
+        <v>1.8186</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3393</v>
+        <v>-0.2701</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0418</v>
+        <v>2.0888</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9627</v>
+        <v>0.9809</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4205</v>
+        <v>1.1516</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3831</v>
+        <v>-0.1706</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2405</v>
+        <v>0.381</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6405</v>
+        <v>1.017</v>
       </c>
       <c r="L3" t="n">
-        <v>1.881</v>
+        <v>-0.636</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2779</v>
+        <v>0.5999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.78</v>
+        <v>0.1346</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5021</v>
+        <v>0.4654</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3748</v>
+        <v>0.0458</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9687</v>
+        <v>-0.1943</v>
       </c>
       <c r="U3" t="n">
-        <v>1.406</v>
+        <v>0.2401</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4599</v>
+        <v>0.5838</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2112</v>
+        <v>0.5838</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>I. DUKE TOUSSAINT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8694</v>
+        <v>1.6409</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0139</v>
+        <v>1.333</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8833</v>
+        <v>0.3078</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9809</v>
+        <v>0.9627</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1516</v>
+        <v>-1.4205</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1706</v>
+        <v>2.3831</v>
       </c>
       <c r="J4" t="n">
-        <v>0.381</v>
+        <v>1.2405</v>
       </c>
       <c r="K4" t="n">
-        <v>1.017</v>
+        <v>-0.6405</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.636</v>
+        <v>1.881</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5999</v>
+        <v>-0.2779</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1346</v>
+        <v>-0.78</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4654</v>
+        <v>0.5021</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0965</v>
+        <v>0.6345</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0619</v>
+        <v>-0.0376</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0346</v>
+        <v>0.672</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5838</v>
+        <v>0.4599</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5838</v>
+        <v>2.2112</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. TSEGAKELE</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5455</v>
+        <v>1.0375</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3882</v>
+        <v>0.4135</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1574</v>
+        <v>0.624</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0124</v>
+        <v>-0.1483</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7634</v>
+        <v>-0.4732</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.249</v>
+        <v>0.3249</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7144</v>
+        <v>0.0968</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7144</v>
+        <v>0.0576</v>
       </c>
       <c r="L5" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.245</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.5308</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
-        <v>-0.298</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.049</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.249</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.6244</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-1.0406</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1823</v>
+        <v>0.5614</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1431</v>
+        <v>0.3167</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0391</v>
+        <v>0.2447</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2477</v>
+        <v>0.4111</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2295</v>
+        <v>-1.9298</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4772</v>
+        <v>2.3408</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1483</v>
+        <v>-0.8837</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4732</v>
+        <v>-1.785</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3249</v>
+        <v>0.9013</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0968</v>
+        <v>-0.8712</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0576</v>
+        <v>-1.1969</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0392</v>
+        <v>0.3257</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.245</v>
+        <v>-0.0125</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5308</v>
+        <v>-0.5881</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2857</v>
+        <v>0.5756</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6244</v>
+        <v>2.2893</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2284</v>
+        <v>0.146</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3262</v>
+        <v>0.082</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0979</v>
+        <v>0.064</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.9813</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.9813</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4151</v>
+        <v>0.3915</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2142</v>
+        <v>0.3868</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2009</v>
+        <v>0.0046</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8911</v>
@@ -1000,13 +1000,13 @@
         <v>2.2893</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9194</v>
+        <v>-1.1129</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.423</v>
+        <v>-0.8219</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4964</v>
+        <v>-0.2909</v>
       </c>
       <c r="V7" t="n">
         <v>0.1061</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>A. TSEGAKELE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4487</v>
+        <v>-0.5745</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5913</v>
+        <v>-0.7906</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1426</v>
+        <v>0.2161</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3008</v>
+        <v>-1.0124</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4478</v>
+        <v>-0.7634</v>
       </c>
       <c r="I8" t="n">
-        <v>0.147</v>
+        <v>-0.249</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3084</v>
+        <v>-0.7144</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0922</v>
+        <v>-0.7144</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7838000000000001</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9924</v>
+        <v>-0.298</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3556</v>
+        <v>-0.049</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6368</v>
+        <v>-0.249</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9137</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q8" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.0623</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.9644</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.9137</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.124</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.5129</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.3889</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.9376</v>
-      </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7089</v>
+        <v>-0.5787</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1085</v>
+        <v>-0.6332</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3995</v>
+        <v>0.0545</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8837</v>
+        <v>-2.3008</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.785</v>
+        <v>-2.4478</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9013</v>
+        <v>0.147</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8712</v>
+        <v>-0.3084</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1969</v>
+        <v>-1.0922</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3257</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0125</v>
+        <v>-1.9924</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5881</v>
+        <v>-1.3556</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5756</v>
+        <v>-0.6368</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8325</v>
+        <v>2.9137</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2893</v>
+        <v>2.9137</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.974</v>
+        <v>-0.254</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0967</v>
+        <v>-0.5548</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1227</v>
+        <v>0.3008</v>
       </c>
       <c r="V9" t="n">
-        <v>1.9813</v>
+        <v>-0.9376</v>
       </c>
       <c r="W9" t="n">
-        <v>1.9813</v>
+        <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9372</v>
+        <v>-2.447</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0993</v>
+        <v>-2.6815</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1621</v>
+        <v>0.2345</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0815</v>
+        <v>-0.2084</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2791</v>
+        <v>0.6415</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1976</v>
+        <v>-0.8499</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0609</v>
+        <v>0.9185</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2177</v>
+        <v>0.8458</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1568</v>
+        <v>0.0726</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0206</v>
+        <v>-1.1269</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0614</v>
+        <v>-0.2043</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0408</v>
+        <v>-0.9225</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1218</v>
+        <v>-4.1624</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0812</v>
+        <v>2.9137</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3524</v>
+        <v>0.6553</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9159</v>
+        <v>0.4563</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4365</v>
+        <v>0.199</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1675</v>
+        <v>-1.6452</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1675</v>
+        <v>0.1061</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3351</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5074</v>
+        <v>-2.5038</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3897</v>
+        <v>-2.3136</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1178</v>
+        <v>-0.1903</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2084</v>
+        <v>-1.0815</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6415</v>
+        <v>-1.2791</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8499</v>
+        <v>0.1976</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9185</v>
+        <v>-1.0609</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8458</v>
+        <v>-1.2177</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0726</v>
+        <v>0.1568</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1269</v>
+        <v>-0.0206</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2043</v>
+        <v>-0.0614</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9225</v>
+        <v>0.0408</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1624</v>
+        <v>-3.1218</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9137</v>
+        <v>2.0812</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4052</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2519</v>
+        <v>0.7016</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1533</v>
+        <v>0.0842</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6452</v>
+        <v>-1.1675</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1061</v>
+        <v>1.1675</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7513</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.757200000000001</v>
+        <v>3.0834</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5636</v>
+        <v>-2.237300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>5.320600000000001</v>
+        <v>5.320399999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6332</v>
@@ -1360,13 +1360,13 @@
         <v>-4.5312</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8981000000000005</v>
+        <v>0.8981</v>
       </c>
       <c r="J12" t="n">
         <v>2.8392</v>
       </c>
       <c r="K12" t="n">
-        <v>1.083799999999999</v>
+        <v>1.0838</v>
       </c>
       <c r="L12" t="n">
         <v>1.7552</v>
@@ -1390,10 +1390,10 @@
         <v>17.6901</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5525</v>
+        <v>1.8788</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2146000000000002</v>
+        <v>0.5409999999999999</v>
       </c>
       <c r="U12" t="n">
         <v>1.3378</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9288</v>
+        <v>2.8675</v>
       </c>
       <c r="E13" t="n">
-        <v>3.178</v>
+        <v>1.9993</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7508</v>
+        <v>0.8682</v>
       </c>
       <c r="G13" t="n">
         <v>0.0866</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6747</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4907</v>
+        <v>0.312</v>
       </c>
       <c r="U13" t="n">
-        <v>0.184</v>
+        <v>0.3014</v>
       </c>
       <c r="V13" t="n">
         <v>1.7513</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8459</v>
+        <v>1.0665</v>
       </c>
       <c r="E14" t="n">
-        <v>2.434</v>
+        <v>2.5411</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5881</v>
+        <v>-1.4746</v>
       </c>
       <c r="G14" t="n">
         <v>2.1636</v>
@@ -1546,13 +1546,13 @@
         <v>0.4162</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1096</v>
+        <v>0.1111</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4567</v>
+        <v>-0.3495</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3471</v>
+        <v>0.4606</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5838</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. KOCIC</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.248</v>
+        <v>-0.0015</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2085</v>
+        <v>-1.6347</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9605</v>
+        <v>1.6331</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.3</v>
+        <v>-0.0453</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3179</v>
+        <v>1.1344</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9822</v>
+        <v>-1.1797</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.618</v>
+        <v>0.4938</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.0604</v>
+        <v>1.3919</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5576</v>
+        <v>-0.8981</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.5391</v>
       </c>
       <c r="N15" t="n">
         <v>-0.2575</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4245</v>
+        <v>-0.2817</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6649</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4495</v>
+        <v>0.3549</v>
       </c>
       <c r="T15" t="n">
-        <v>0.242</v>
+        <v>-0.1743</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2075</v>
+        <v>0.5292</v>
       </c>
       <c r="V15" t="n">
         <v>0.9376</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>V. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6374</v>
+        <v>-0.3669</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.9269</v>
+        <v>-1.0931</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2895</v>
+        <v>0.7262</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3051</v>
+        <v>2.5554</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4669</v>
+        <v>2.4672</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1618</v>
+        <v>0.0882</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0463</v>
+        <v>2.3924</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1114</v>
+        <v>2.2022</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1577</v>
+        <v>0.1902</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3514</v>
+        <v>0.163</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3555</v>
+        <v>0.265</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0041</v>
+        <v>-0.102</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.0406</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1218</v>
+        <v>-3.3299</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0812</v>
+        <v>2.7055</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0007</v>
+        <v>-0.3167</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.019</v>
+        <v>-0.1557</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0197</v>
+        <v>-0.161</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7076</v>
+        <v>-1.9813</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4599</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6736</v>
+        <v>-0.3771</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1821</v>
+        <v>-1.9269</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5084</v>
+        <v>1.5498</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3385</v>
+        <v>-0.3051</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1107</v>
+        <v>-1.4669</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2278</v>
+        <v>1.1618</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6202</v>
+        <v>0.0463</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5026</v>
+        <v>-1.1114</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1176</v>
+        <v>1.1577</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7183</v>
+        <v>-0.3514</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6081</v>
+        <v>-0.3555</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1102</v>
+        <v>0.0041</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8731</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.3299</v>
+        <v>-3.1218</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2584</v>
+        <v>0.261</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4724</v>
+        <v>-0.019</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7308</v>
+        <v>0.28</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3975</v>
+        <v>0.7076</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3975</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>S. KOCIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7785</v>
+        <v>-0.3845</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0633</v>
+        <v>-1.3157</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2847</v>
+        <v>0.9312</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0453</v>
+        <v>-3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1344</v>
+        <v>-2.3179</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1797</v>
+        <v>-0.9822</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4938</v>
+        <v>-2.618</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3919</v>
+        <v>-2.0604</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8981</v>
+        <v>-0.5576</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5391</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>-0.2575</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2817</v>
+        <v>-0.4245</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4221</v>
+        <v>0.313</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6029</v>
+        <v>0.1348</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1808</v>
+        <v>0.1782</v>
       </c>
       <c r="V18" t="n">
         <v>0.9376</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0783</v>
+        <v>-0.6584</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5372</v>
+        <v>-0.3229</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5411</v>
+        <v>-0.3356</v>
       </c>
       <c r="G19" t="n">
         <v>0.9748</v>
@@ -1936,13 +1936,13 @@
         <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3851</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5219</v>
+        <v>-0.3076</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8631</v>
+        <v>-0.6576</v>
       </c>
       <c r="V19" t="n">
         <v>-0.4599</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0887</v>
+        <v>-0.8935</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3765</v>
+        <v>-0.2694</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.6241</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3894</v>
@@ -2014,13 +2014,13 @@
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8638</v>
+        <v>-0.6685</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4723</v>
+        <v>-0.3842</v>
       </c>
       <c r="V20" t="n">
         <v>-0.4599</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. MORENO MARTIN</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1527</v>
+        <v>-0.9917</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7361</v>
+        <v>-1.9678</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5833</v>
+        <v>0.976</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5554</v>
+        <v>2.3385</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4672</v>
+        <v>2.1107</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0882</v>
+        <v>0.2278</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3924</v>
+        <v>1.6202</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2022</v>
+        <v>1.5026</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1902</v>
+        <v>0.1176</v>
       </c>
       <c r="M21" t="n">
-        <v>0.163</v>
+        <v>0.7183</v>
       </c>
       <c r="N21" t="n">
-        <v>0.265</v>
+        <v>0.6081</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.102</v>
+        <v>0.1102</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6244</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q21" t="n">
         <v>-3.3299</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7055</v>
+        <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1025</v>
+        <v>-0.0597</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7986</v>
+        <v>-0.2581</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3039</v>
+        <v>0.1984</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.9813</v>
+        <v>-1.3975</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9813</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="22">
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8744</v>
+        <v>-2.303</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.902</v>
+        <v>-1.3306</v>
       </c>
       <c r="F22" t="n">
         <v>-0.9724</v>
@@ -2170,10 +2170,10 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0529</v>
+        <v>-0.4815</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1924</v>
+        <v>-0.2362</v>
       </c>
       <c r="U22" t="n">
         <v>-0.2453</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.756899999999999</v>
+        <v>-2.042599999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3206</v>
+        <v>-5.3207</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5634</v>
+        <v>3.2778</v>
       </c>
       <c r="G23" t="n">
         <v>3.6332</v>
       </c>
       <c r="H23" t="n">
-        <v>4.531099999999999</v>
+        <v>4.5311</v>
       </c>
       <c r="I23" t="n">
         <v>-0.8981000000000001</v>
@@ -2224,7 +2224,7 @@
         <v>6.4722</v>
       </c>
       <c r="K23" t="n">
-        <v>5.614999999999998</v>
+        <v>5.614999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>0.8573</v>
@@ -2248,19 +2248,19 @@
         <v>14.5682</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5527</v>
+        <v>-0.8381999999999998</v>
       </c>
       <c r="T23" t="n">
         <v>-1.3379</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2147</v>
+        <v>0.4997000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7158</v>
       </c>
       <c r="W23" t="n">
-        <v>7.2351</v>
+        <v>7.235099999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-8.9511</v>
